--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2BE3EB-2747-48D1-9722-5B9A75E097DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC75E5A-DD2A-43E6-9C37-80694D0449E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="153">
   <si>
     <t>Problem Name</t>
   </si>
@@ -334,6 +334,156 @@
   </si>
   <si>
     <t>check for the elements left in the stack after updating maxHeight in a separate loop..</t>
+  </si>
+  <si>
+    <t>BINARY TREE</t>
+  </si>
+  <si>
+    <t>Max depth</t>
+  </si>
+  <si>
+    <t>Assign variables to left and right recursive call and return max(left, right) + 1;</t>
+  </si>
+  <si>
+    <t>Invert binary tree</t>
+  </si>
+  <si>
+    <t>use postorder traversal, at the time of root node swap the left and right subtrees using temp node.</t>
+  </si>
+  <si>
+    <t>Balanced binary tree</t>
+  </si>
+  <si>
+    <t>At any point, if abs(lh-rh)&gt;1 then return -1, check lh and rh after every recursive call if lh==-1 or rh==-1 then return -1, at the end return max(lh,rh)+1;</t>
+  </si>
+  <si>
+    <t>returns the height of the tree if it is balanced else returns -1;</t>
+  </si>
+  <si>
+    <t>Diameter of tree</t>
+  </si>
+  <si>
+    <t>Naïve: calculate height of left tree and right tree and return the sum of both;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">optimal: use another global variable diameter that computes the diameter at each of the node, calculate the height of the node and max diameter in single </t>
+  </si>
+  <si>
+    <t>function.</t>
+  </si>
+  <si>
+    <t>Same tree</t>
+  </si>
+  <si>
+    <t>Subtree</t>
+  </si>
+  <si>
+    <t>Easy/medium</t>
+  </si>
+  <si>
+    <t>use helper function sameTree. Lot of</t>
+  </si>
+  <si>
+    <t>Keep in mind the edge cases, if root is null, if subtree is null, if both are null if one is null.</t>
+  </si>
+  <si>
+    <t>Lowest common ans of bst</t>
+  </si>
+  <si>
+    <t>if p and q &lt; root then traverse left tree, if p and q&gt; root then traverse right tree, if none then return root.</t>
+  </si>
+  <si>
+    <t>LCA of binary tree</t>
+  </si>
+  <si>
+    <t>base case is root==null or root==p or root==q then return root.</t>
+  </si>
+  <si>
+    <t>if lh is null then ancestor is in right tree, if rh is null then ancestor is in the left tree, else the current node is the ancestor</t>
+  </si>
+  <si>
+    <t>Right view of binary tree</t>
+  </si>
+  <si>
+    <t>base cases are both the nodes are null then return true and if one node is null then return false. If pval==qval return true and recursively traverse left and right tree is all conditions are true.</t>
+  </si>
+  <si>
+    <t>BFS :  last element of each array in level order traversal</t>
+  </si>
+  <si>
+    <t>DFS :</t>
+  </si>
+  <si>
+    <t>Count good nodes</t>
+  </si>
+  <si>
+    <t>Declare 2 variables which stores currentMax dn goodNodes. Base case: if current node is NULL return goodNodes. If root-&gt;val &gt;= currentMax then goodNodes++, update the current max and traverse left and right.</t>
+  </si>
+  <si>
+    <t>use void recursive helper function, store the answer in a global variable in the main function and return the ans in the main function</t>
+  </si>
+  <si>
+    <t>recursion : base case -&gt; logic with base case -&gt; recursive calls -&gt; return call(if the function is int function)</t>
+  </si>
+  <si>
+    <t>Construct BST from preorder</t>
+  </si>
+  <si>
+    <t>or another solution: initialize null node, use for loop to pass the preorder elements into the node using helper function, if data&gt;node-&gt;val insert to right else insert into left tree.</t>
+  </si>
+  <si>
+    <t>base case: when we reach a null node, then assign a new node to that place with val and return node i.e if node==NULL then node=new Node(data) return node;</t>
+  </si>
+  <si>
+    <t>don’t forget to assign variable root-&gt;right, root-&gt;left to recursive calls as it will update the current root-&gt;val to compare the data to be inserted.s</t>
+  </si>
+  <si>
+    <t>Distance between two nodes in bt</t>
+  </si>
+  <si>
+    <t>Valid BST</t>
+  </si>
+  <si>
+    <t>Use store inorder in array and see if elements are in sorted order</t>
+  </si>
+  <si>
+    <t>patterns: max depth, level order traversal, same tree concept, subtree concept, maintaining currSum of nodes concept(path sum), LCA</t>
+  </si>
+  <si>
+    <t>Distance from to node from root</t>
+  </si>
+  <si>
+    <t>use int function, base case if root is null then return -1 and if root is target return level. Traverse left tree then if d=-1(not found) then traverse right tree.</t>
+  </si>
+  <si>
+    <t>find lca of the two nodes, find distance from lca to both nodes separately and then add.</t>
+  </si>
+  <si>
+    <t>check if root&lt;upper AND root&gt;lower then call recursion with max of left tree as root-&gt;val AND  max of right tree as INT_MAX else return false.</t>
+  </si>
+  <si>
+    <t>Kth smallest in bst</t>
+  </si>
+  <si>
+    <t>Stack: push elements in stack and when k=0; return the top element; (BEATS 99%)</t>
+  </si>
+  <si>
+    <t>Naïve: make inorder traversal array, return k-1th element as it is sorted in ascending order. (BEATS 12%)</t>
+  </si>
+  <si>
+    <t>Make bt from preorder and inorder</t>
+  </si>
+  <si>
+    <t>Concept: first element of preorder is always the node, elements to the left of element in inorder are left tree elements and to the right are right tree elements</t>
+  </si>
+  <si>
+    <t>Naïve: use two variables to divide the inorder array into left and then right, use 3rd variable to traverse preorder,when preorder[index]==inorder[i] then set mid=index and</t>
+  </si>
+  <si>
+    <t>pass the left subarray into left tree and right subarray into right tree (BAD RUNTIME)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimized approach: make hashmap of index of inorder array, use 4 variables for start and end of both arrays, base case: prestart&gt;preend||instart&gt;inend, calc no. of elements left using hashmap indices and </t>
   </si>
 </sst>
 </file>
@@ -753,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1271,6 +1421,265 @@
         <v>102</v>
       </c>
     </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B111" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C118" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C121" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C127" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C132" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C135" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C139" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C140" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C143" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C144" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C150" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C153" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C157" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C158" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C160" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC75E5A-DD2A-43E6-9C37-80694D0449E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC43656-5002-46D1-B256-B29E9F13F454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="177">
   <si>
     <t>Problem Name</t>
   </si>
@@ -369,9 +369,6 @@
     <t xml:space="preserve">optimal: use another global variable diameter that computes the diameter at each of the node, calculate the height of the node and max diameter in single </t>
   </si>
   <si>
-    <t>function.</t>
-  </si>
-  <si>
     <t>Same tree</t>
   </si>
   <si>
@@ -484,6 +481,81 @@
   </si>
   <si>
     <t xml:space="preserve">Optimized approach: make hashmap of index of inorder array, use 4 variables for start and end of both arrays, base case: prestart&gt;preend||instart&gt;inend, calc no. of elements left using hashmap indices and </t>
+  </si>
+  <si>
+    <t>Max path Sum</t>
+  </si>
+  <si>
+    <t>we return root-&gt;val+max(left,right) to include the maximum path sum of left or right subtree of a given node IF WE DO NOT wish to include the curretn node's value.</t>
+  </si>
+  <si>
+    <t>If any of the left or right child is -ve then set it to zero, maintain currSum(differs for each node) and maxSum(global), at the end return root-&gt;val+max(left,right)</t>
+  </si>
+  <si>
+    <t>exclude -ve values by storing the recursive calls in a variable as left=max(dfs(root-&gt;left, maxSum), 0);</t>
+  </si>
+  <si>
+    <t>function, BASICALLY ADD A CONDITION TO CHECK THE MAXIMUM DEPTH OF LH AND RH AT EACH RECURSIVE CALL</t>
+  </si>
+  <si>
+    <t>Serialize and deserialize</t>
+  </si>
+  <si>
+    <t>Use istringstream, ostringstream and delimited and preorder dfs</t>
+  </si>
+  <si>
+    <t>do it again did not understand stringstream functions.</t>
+  </si>
+  <si>
+    <t>Optimal : use preorder and queues and string encoding function. Use delimiter "," and "X," to encode.</t>
+  </si>
+  <si>
+    <t>PRIORITY QUEUE</t>
+  </si>
+  <si>
+    <t>K closest points to the origin</t>
+  </si>
+  <si>
+    <t>Naïve: make vector&lt;pair&lt;int, int&gt;&gt; which stores &lt;distance from origin, index in points array&gt;, sort them in ascending order, push first k elements to answer array.</t>
+  </si>
+  <si>
+    <t>Naïve: use 2d array to store triplets &lt;dist, point1, point2&gt;, use min heap to push triplets into it, remove top k triplets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimal : Use quick select (version of quick sort), </t>
+  </si>
+  <si>
+    <t>kth largest element in array</t>
+  </si>
+  <si>
+    <t>Naïve: make max heap, pop till k-1 and top.</t>
+  </si>
+  <si>
+    <t>Optimal: quickselect, kth largest from right side would be nums.size()-k from left, use quick sort loops and variables and at the end if k&gt;j then return right subarray, if k&lt;j return left sub else return nums[j].</t>
+  </si>
+  <si>
+    <t>it basically sorts the array in place and checks if the cureent element is the kth largest or not.</t>
+  </si>
+  <si>
+    <t>task scheduler</t>
+  </si>
+  <si>
+    <t>use maxheap to store the frequency of characters, use queue&lt;vector&lt;int&gt;&gt; to store the (tasks left of character,time taken+n)</t>
+  </si>
+  <si>
+    <t>pop from heap and push to queue, pop from queue and ush to heap</t>
+  </si>
+  <si>
+    <t>DO IT AGAIN</t>
+  </si>
+  <si>
+    <t>Design twitter</t>
+  </si>
+  <si>
+    <t>Use vector&lt;pair&lt;int,int&gt;&gt; for posts (userid, tweetid), use unordered_map&lt;int, unordered_set&lt;int&gt;&gt; for followers, keep in mind the posts should be &lt;10 and most recent should be shown first(use max heap or</t>
+  </si>
+  <si>
+    <t>traverse from end) and feed should show the followers feed as well as the current users feed, traverse posts for each followerId in the followingUsers set.</t>
   </si>
 </sst>
 </file>
@@ -903,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1426,7 +1498,7 @@
         <v>103</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -1453,13 +1525,13 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -1496,188 +1568,314 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C122" s="1" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="C126" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C127" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C132" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C135" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C139" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C140" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C143" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C144" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C150" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C153" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C157" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C158" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C160" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
         <v>152</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C164" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C165" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C168" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C169" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B172" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C175" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C176" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C179" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C180" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C183" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C184" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C187" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC43656-5002-46D1-B256-B29E9F13F454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C8C726-FFF0-49F5-9DD4-F0939EEB6369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="180">
   <si>
     <t>Problem Name</t>
   </si>
@@ -556,6 +556,15 @@
   </si>
   <si>
     <t>traverse from end) and feed should show the followers feed as well as the current users feed, traverse posts for each followerId in the followingUsers set.</t>
+  </si>
+  <si>
+    <t>Median from stream of data</t>
+  </si>
+  <si>
+    <t>Use two heaps, maxHeap to store smaller sorted elements and minHeap to store larger sorted elements.</t>
+  </si>
+  <si>
+    <t>Make sure to balance the heaps whenever data is inserted, if size is equal that means dataset has even numbers else they have odd numbers</t>
   </si>
 </sst>
 </file>
@@ -975,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1878,6 +1887,22 @@
         <v>176</v>
       </c>
     </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C190" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C8C726-FFF0-49F5-9DD4-F0939EEB6369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DEA99D-D5D5-4A64-850C-EE0CA1102AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
   <si>
     <t>Problem Name</t>
   </si>
@@ -565,6 +565,87 @@
   </si>
   <si>
     <t>Make sure to balance the heaps whenever data is inserted, if size is equal that means dataset has even numbers else they have odd numbers</t>
+  </si>
+  <si>
+    <t>Backtracking</t>
+  </si>
+  <si>
+    <t>Subsets</t>
+  </si>
+  <si>
+    <t>two cases are to include the next element and not to include the next element. Base case is when the input size is 0, in each call increment the output with the first element of input, erase the input's first element</t>
+  </si>
+  <si>
+    <t>call two recursive calls in which one excludes the next element and one includes the next element.(BAD TC)</t>
+  </si>
+  <si>
+    <t>Optimal: use DFS approach, use for loop inside the recusive function to iterate over the array elements, include the elements then make recursive call by incrementing the start index and then pop the elements.</t>
+  </si>
+  <si>
+    <t>include one and exclude one principle, the recursive call inside the for loop is basically to traverse to the end of the array from the current position.</t>
+  </si>
+  <si>
+    <t>Permutations</t>
+  </si>
+  <si>
+    <t>QUITE CONFUSING, total subsets = 2^n</t>
+  </si>
+  <si>
+    <t>swap i and start, use swap concept, total permutations = 2*n</t>
+  </si>
+  <si>
+    <t>number of divides = number of elements in the array, swap current element with each element including itself.</t>
+  </si>
+  <si>
+    <t>Combinations(duplicates allowed)</t>
+  </si>
+  <si>
+    <t>Base cases : i==size of array, target&lt;0 and target==0, similar to subsets, first check if including the current element again sums to the target then recursively call the dfs function with target=target-combination[i]</t>
+  </si>
+  <si>
+    <t>if not, then pop_back the element and call dfs with target untouched and i+1;</t>
+  </si>
+  <si>
+    <t>Subsets II (with duplicates)</t>
+  </si>
+  <si>
+    <t>Sort initial array, use for loop with i&lt;start concept to avoid duplicates., similar to combination sum.</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>when given duplicates, use the i&lt;start and for loop method or use the set to ignore the duplicate values.</t>
+  </si>
+  <si>
+    <t>Combination(no duplicates)</t>
+  </si>
+  <si>
+    <t>base case target&lt;0 then return, target==0 then push into result, use for loop i&lt;start method to ignore duplicates.</t>
+  </si>
+  <si>
+    <t>Word search</t>
+  </si>
+  <si>
+    <t>Search for the first character of the word to be found in the grid, pass the current i and j to dfs function an index to keep track of the characters of the word.</t>
+  </si>
+  <si>
+    <t>Base case : i&lt;0 or i&gt;=rows || j&lt;0 || j&gt;=cols || board[i][j]!=word[index] then return false, if index==word.size()-1 then return true</t>
+  </si>
+  <si>
+    <t>mark the current board[i][j] as visited using some character ( use '#')</t>
+  </si>
+  <si>
+    <t>make 4 variables up,down,left,right to store the results of the recursive calls in all four directions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if up or down or left or right is true, then return true </t>
+  </si>
+  <si>
+    <t>else at the end, replace board[i][j]=word[index] witht the original character and return false.</t>
+  </si>
+  <si>
+    <t>Optimization: if the first word is repeating more than the last word, then feed the reverse of the word into dfs as we will have to call recursion less number of times(pruning).</t>
   </si>
 </sst>
 </file>
@@ -984,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1903,6 +1984,145 @@
         <v>179</v>
       </c>
     </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B194" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C197" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C198" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C199" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C200" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C203" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C206" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B212" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C219" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C220" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C221" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C222" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C223" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C225" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DEA99D-D5D5-4A64-850C-EE0CA1102AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBD2DAA-2E24-4358-9944-C253F1C2A0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="221">
   <si>
     <t>Problem Name</t>
   </si>
@@ -615,9 +615,6 @@
     <t>NOTE</t>
   </si>
   <si>
-    <t>when given duplicates, use the i&lt;start and for loop method or use the set to ignore the duplicate values.</t>
-  </si>
-  <si>
     <t>Combination(no duplicates)</t>
   </si>
   <si>
@@ -646,6 +643,51 @@
   </si>
   <si>
     <t>Optimization: if the first word is repeating more than the last word, then feed the reverse of the word into dfs as we will have to call recursion less number of times(pruning).</t>
+  </si>
+  <si>
+    <t>GRAPHS</t>
+  </si>
+  <si>
+    <t>Number of islands</t>
+  </si>
+  <si>
+    <t>dfs + count variable, base case = out of bounds(4 conditions) || grid[i][j]=='0', then recursive for all 4 dirns,   basically check how many times the dfs function is called inside the traversal of the grid ie when "1" is found</t>
+  </si>
+  <si>
+    <t>Palindromic partitioning</t>
+  </si>
+  <si>
+    <t>dfs, base case if start==s.size() then push into ans vector, use another helper function to check if the current substring is a palindrome or not, if it is palidrome only then add the substr else no.</t>
+  </si>
+  <si>
+    <t>a bit tough do it again.</t>
+  </si>
+  <si>
+    <t>Combinations</t>
+  </si>
+  <si>
+    <t>Combinations = n*m, same push loop pop pattern, base case, curr.size()==k, make a temp array in which 1 to n numbers are stored then pass to dfs function.</t>
+  </si>
+  <si>
+    <t>Letter comb of phone numbers</t>
+  </si>
+  <si>
+    <t>use map&lt;char,string&gt;, extract the string belonging to the current index in the function, same push loop pop pattern but instead of incrementing i , we increment start. Base case: start==digits.size()</t>
+  </si>
+  <si>
+    <t>push loop pop pattern: when the dfs inside the for loop is called, the base case condition returns true, then the added element gets popped and the for loop moves to next iteration.</t>
+  </si>
+  <si>
+    <t>when given duplicates, use the i&lt;start&amp;&amp;nums[i]!=nums[i-1] and for loop method or use the set to ignore the duplicate values.</t>
+  </si>
+  <si>
+    <t>Flood fill</t>
+  </si>
+  <si>
+    <t>dfs, base case: boundary conditions(4), current cell==start or current cell==color then return, mark current cell as new color, traverse all 4 directions</t>
+  </si>
+  <si>
+    <t>Flood fill is a concept in which we traverse to all the neighbours having the same value as the current cell and ignore the different value cells.</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1988,6 +2030,9 @@
       <c r="B194" s="3" t="s">
         <v>180</v>
       </c>
+      <c r="C194" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
@@ -2068,59 +2113,129 @@
         <v>195</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C219" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C220" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C221" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C222" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C223" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C225" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C225" s="1" t="s">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C228" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B240" s="3" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C245" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/Leetcode aug.xlsx
+++ b/Leetcode aug.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishabh Sharma\Desktop\dev 2023 aug\Leetcode Aug 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBD2DAA-2E24-4358-9944-C253F1C2A0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D602B8-E823-4E43-B44F-1D690C95C92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{533DFAC3-83F0-4B29-9134-E1375E256C4B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="283">
   <si>
     <t>Problem Name</t>
   </si>
@@ -183,9 +183,6 @@
     <t>basically, right pointer is used to increase the length and left is used to delete the repeated character represented by right.</t>
   </si>
   <si>
-    <t>left starts from 0 and right starts either from 0 or 1 / mostly used in addition with sets or hashmaps</t>
-  </si>
-  <si>
     <t>Permutation in string</t>
   </si>
   <si>
@@ -688,6 +685,195 @@
   </si>
   <si>
     <t>Flood fill is a concept in which we traverse to all the neighbours having the same value as the current cell and ignore the different value cells.</t>
+  </si>
+  <si>
+    <t>Island perimeter</t>
+  </si>
+  <si>
+    <t>For each 1, add 4 to the final ans, check if there is an island on the top and left then subtract 2 for each case.</t>
+  </si>
+  <si>
+    <t>dfs, mark visited as -1, if current cell if out of bounds or 0, then ans++, recursive call for all 4 directions.</t>
+  </si>
+  <si>
+    <t>N queens</t>
+  </si>
+  <si>
+    <t>Mountain array</t>
+  </si>
+  <si>
+    <t>if arr[mid]&lt;arr[mid+1] then left=mid+1 else right=mid-1 , peak of mountain array is stored in left.</t>
+  </si>
+  <si>
+    <t>the condition for the left array of the peak and right array of the peak change.</t>
+  </si>
+  <si>
+    <t>Rotten Oranges</t>
+  </si>
+  <si>
+    <t>BFS(as we need to explore neighbours), use queue&lt;pair&lt;pair&lt;int,int&gt;,int&gt;&gt; and visited matrix, look for 2 in the grid and push it to the queue also maintain a counter of 1's to check at the last.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">use delrow=[-1,0,1,0} and delcol=[0,1,0,-1] to explore all 4 neighbours, declare nrow and ncol, check 4 boundary conditions &amp;&amp; vis[nrow][col]!=2 &amp;&amp; grid[nrow][ncol]==1 then push to queue, mark as visited and </t>
+  </si>
+  <si>
+    <t>increment the 1's counter.</t>
+  </si>
+  <si>
+    <t>REDO AFTER 2 WEEKS.</t>
+  </si>
+  <si>
+    <t>DFS</t>
+  </si>
+  <si>
+    <t>Use recursion, with ans vector, start index, visited array and adjacency list. Mark current node as visited, push into ans, and use for loop to traverse neighbours</t>
+  </si>
+  <si>
+    <t>Use queue, visited array, adjacency list. Push 0 into the queue and mark 0 as visited and traverse its neighbours while the q is not empty.</t>
+  </si>
+  <si>
+    <t>BFS</t>
+  </si>
+  <si>
+    <t>Detecting cycle(union find)</t>
+  </si>
+  <si>
+    <t>Bfs + queue&lt;pair&lt;int,int&gt;&gt; to store (node, parent), when pushing to the queue, just check else if(parent!=it) return true; (cycle detected)</t>
+  </si>
+  <si>
+    <t>don’t forget to call the initial bfs call inside the for loop to also include Disconnected components.</t>
+  </si>
+  <si>
+    <t>Maximum area of island</t>
+  </si>
+  <si>
+    <t>DFS : use same concept as finding max height of binary tree i.e return 1+right+left+up+down</t>
+  </si>
+  <si>
+    <t>01 matrix</t>
+  </si>
+  <si>
+    <t>BFS, store ((row,col),dist), use 2d vis matrix and 2d dist matrix, initially push all the cells with 0 and distance 0, start bfs, update the dist matrix by dist, increment distance by one if pushing into the queue.</t>
+  </si>
+  <si>
+    <t>BFS,DFS on grid and BFS DFS on adjacency lists(graphs)</t>
+  </si>
+  <si>
+    <t>Pacific atlantic water flow</t>
+  </si>
+  <si>
+    <t>j-i+1 is the window size.</t>
+  </si>
+  <si>
+    <t>Grid DFS BFS</t>
+  </si>
+  <si>
+    <t>Boundary problems, if some cells are connected to the boundary of the grid, then they can or can not be included in the answer.</t>
+  </si>
+  <si>
+    <t>ex: surrounded regions, 01 matrix, number of enclaves, number of distinct islands</t>
+  </si>
+  <si>
+    <t>BFS/DFS, Tricky implementation, main logic is to maintain two separate visited arrays for pacific and atlantic and go in from the boundaries, the 1's which occur in both arrays are answers.</t>
+  </si>
+  <si>
+    <t>the condition gets reversed if we go from out to in, the neighbouring element must be greater than the current element.</t>
+  </si>
+  <si>
+    <t>Surrounded regions</t>
+  </si>
+  <si>
+    <t>in the answer matrix, if current cell is 1 then mark as 0 else mark as X.</t>
+  </si>
+  <si>
+    <t>DFS from boundary 0s, the inner 0s connected to the boundary 0s can never be surrounded, mark all these connected inner and boundary 0s as visited in the vis matrix</t>
+  </si>
+  <si>
+    <t>For directed graph, use additional isPathVisited array to check if the neighbour is already visited AND it is in the same path, then return true, do isPathVisited[i]=0 at the end of recursive loop</t>
+  </si>
+  <si>
+    <t>striver graph series + neetcode</t>
+  </si>
+  <si>
+    <t>Eventual safe states</t>
+  </si>
+  <si>
+    <t>Can also use DFS with parent variable, if the current neighbour is visited and IT IS NOT A PARENT (it!=parent) then return true(cycle found), don’t forget to call the dfs inside the for loop too in the recursive function.</t>
+  </si>
+  <si>
+    <t>DFS + cycle detection in directed graph + checking if pathVis is 0 then it is safe(no cycles) else unsafe(1) OR topological sort(bfs+indegrees)</t>
+  </si>
+  <si>
+    <t>Topological sort</t>
+  </si>
+  <si>
+    <t>can use DFS or BFS(kahns algo), Conditions: graph should be DAG, no cycles in graph. Used in network routing, course scheduling, cases where v DEPENDS on u and u comes BEFORE v.</t>
+  </si>
+  <si>
+    <t>for any adjacency list element if u-&gt;v then u should appear before in the final answer vector.</t>
+  </si>
+  <si>
+    <t>BFS(Kahn's) : calculate indegree, push indegree 0 nodes into queue, push current node into answer array,decrement indegree of each neighbour, if indegree is 0 then push into queue.</t>
+  </si>
+  <si>
+    <t>Course Schedule</t>
+  </si>
+  <si>
+    <t>use topological sort using kahns algo, return topo.size()==n</t>
+  </si>
+  <si>
+    <t>use cycle detection method using dfs</t>
+  </si>
+  <si>
+    <t>some variable sliding window questions like subarray sum equals to k, subarray divisible by k requires us to use prefix sum with a map.</t>
+  </si>
+  <si>
+    <t>left starts from 0 and right starts either from 0 or 1 / mostly used in addition with sets or hashmaps, either find window size(variable) or ans(fixed,k given in ques)</t>
+  </si>
+  <si>
+    <t>Kth symbol in grammar</t>
+  </si>
+  <si>
+    <t>first half of the nth string is exactly same as the whole (n-1)th string, the later half part of nth row is the complement of (n-1)th row and length of nth row is double of (n-1)th row.</t>
+  </si>
+  <si>
+    <t>use 1&lt;&lt;(n-2) to calculate the complement and call !(n-1, k-length) if k&gt;n/2;</t>
+  </si>
+  <si>
+    <t>Course Schedule 2</t>
+  </si>
+  <si>
+    <t>topo sort and return the topo vector.</t>
+  </si>
+  <si>
+    <t>Cycle detection in directed graph</t>
+  </si>
+  <si>
+    <t>DFS + pathVis array…....... Topo sort with topo.size()==n(BFS)</t>
+  </si>
+  <si>
+    <t>we only reset pathVis of a node to 0 again if it is safe else let it be 1(unsafe)</t>
+  </si>
+  <si>
+    <t>Alien dictionary</t>
+  </si>
+  <si>
+    <t>topological sort, if one char1 comes before another char2(in sorted dictionary) then there is a directed edge char1 ---&gt; char2.</t>
+  </si>
+  <si>
+    <t>store each char as an integer i.e adj[dict[i] - 'a'].</t>
+  </si>
+  <si>
+    <t>Shortest dist in DAG</t>
+  </si>
+  <si>
+    <t>DFS: use simple dfs traversal with a stack to store the last visited node at the bottom of the stack, push node into stack at the end of the loop (all nodes will come before that).</t>
+  </si>
+  <si>
+    <t>DFS: use toposort w stack, push all elements into stack in topological order, while the stack is not empty, create a dist array initialized to INT_MAX, update the dist of source to 0, then update the dist of each</t>
+  </si>
+  <si>
+    <t>node in the loop.</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0740D5-EE01-450A-BE0C-92F28A0CBF6A}">
-  <dimension ref="A1:C245"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.21875" style="2" customWidth="1"/>
@@ -1334,7 +1520,12 @@
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>52</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -1374,868 +1565,1193 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="C53" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C90" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C91" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C92" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C97" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C103" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C104" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C107" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C108" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B111" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C118" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C120" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C121" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C122" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="C126" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C127" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C132" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C135" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C139" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C140" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C143" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C144" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C150" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C153" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C157" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C158" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C160" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C164" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C165" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C168" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C169" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B172" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C175" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C176" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C179" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C180" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C183" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C184" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C187" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C190" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B194" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C197" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C198" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C199" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C200" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C203" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C205" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C206" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B212" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C219" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C220" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C221" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C222" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C223" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C225" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C228" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C232" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>215</v>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C237" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B240" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C241" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C245" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="2" t="s">
         <v>220</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C248" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C251" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C252" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C253" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C259" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C260" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C261" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C267" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C269" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C272" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C275" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C277" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C278" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C279" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C282" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C288" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C291" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
